--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainTypicalGeologySurvey.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainTypicalGeologySurvey.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27260" windowHeight="11920"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="主线典型地质勘察" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -43,9 +43,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -68,6 +68,43 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -75,31 +112,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -113,96 +135,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -212,12 +144,80 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -240,25 +240,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,151 +402,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,8 +446,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -455,23 +455,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,176 +526,167 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainTypicalGeologySurvey.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainTypicalGeologySurvey.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27260" windowHeight="11920"/>
+    <workbookView windowWidth="27260" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="主线典型地质勘察" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -19,22 +19,44 @@
     <t>主线位置</t>
   </si>
   <si>
-    <t>业主提供-深度</t>
+    <t>业主提供地勘报告</t>
   </si>
   <si>
-    <t>业主提供-地质描述</t>
-  </si>
-  <si>
-    <t>项目部提供-深度</t>
-  </si>
-  <si>
-    <t>项目部提供-地质描述</t>
-  </si>
-  <si>
-    <t>项目部提供-勘察方式</t>
+    <r>
+      <t>项目部提供</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深度</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>深度（m）</t>
+  </si>
+  <si>
+    <t>地质描述</t>
+  </si>
+  <si>
+    <t>勘察方式</t>
   </si>
 </sst>
 </file>
@@ -42,12 +64,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -63,8 +85,10 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="方正书宋_GBK"/>
       <charset val="134"/>
     </font>
     <font>
@@ -90,18 +114,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -112,9 +129,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -135,6 +167,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -143,80 +236,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -240,13 +271,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -258,85 +379,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,73 +439,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,16 +460,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -461,26 +492,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,6 +527,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,162 +571,147 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -690,14 +721,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1019,8 +1056,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="16.7211538461538" customWidth="1"/>
     <col min="3" max="3" width="22.0384615384615" customWidth="1"/>
@@ -1034,35 +1071,46 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1"/>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="G2" s="1"/>
     </row>
-    <row r="2" ht="14" customHeight="1" spans="1:7">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
+    <row r="3" ht="14" customHeight="1"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="G1:G2"/>
+  </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
